--- a/result/train_info_resnet18_part_detrend_plr_stft_bin_win_pca.xlsx
+++ b/result/train_info_resnet18_part_detrend_plr_stft_bin_win_pca.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>train_loss</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>test_loss</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>test_acc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
@@ -480,28 +468,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4511389360606759</v>
+        <v>0.4411626928894162</v>
       </c>
       <c r="C2" t="n">
         <v>0.001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4680856213238112</v>
+        <v>0.3635977107215915</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8010033444816054</v>
+        <v>0.8439241917502787</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9694171956145412</v>
+        <v>0.9049694856146469</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6226834692364714</v>
+        <v>0.7694588584136397</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7582938388625592</v>
+        <v>0.8317307692307693</v>
       </c>
       <c r="I2" t="n">
-        <v>55.96347379684448</v>
+        <v>35.54265689849854</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +497,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2143598412610535</v>
+        <v>0.2216242663949772</v>
       </c>
       <c r="C3" t="n">
         <v>0.0009997532801828658</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1345088966852109</v>
+        <v>0.2875966192085362</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9533630620587142</v>
+        <v>0.8803418803418803</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9601353892440767</v>
+        <v>0.9659709618874773</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9462564862861379</v>
+        <v>0.7891030392883618</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9531454172111257</v>
+        <v>0.868625050999592</v>
       </c>
       <c r="I3" t="n">
-        <v>56.70552444458008</v>
+        <v>34.99078989028931</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +526,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1204635859577796</v>
+        <v>0.1284363963080772</v>
       </c>
       <c r="C4" t="n">
         <v>0.0009990133642141358</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08216266049975915</v>
+        <v>0.09454323679825963</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9700854700854701</v>
+        <v>0.9633965068747677</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9792217604835664</v>
+        <v>0.9477264590046545</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9607116382505559</v>
+        <v>0.9810971089696071</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9698783910196446</v>
+        <v>0.9641231105445274</v>
       </c>
       <c r="I4" t="n">
-        <v>56.96231031417847</v>
+        <v>35.11249113082886</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +555,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.07623047842076781</v>
+        <v>0.08272028559394026</v>
       </c>
       <c r="C5" t="n">
         <v>0.00099778098230154</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08361016154584072</v>
+        <v>0.07123146632950775</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9659977703455964</v>
+        <v>0.9751021924934968</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9933307179285995</v>
+        <v>0.9926979246733282</v>
       </c>
       <c r="G5" t="n">
-        <v>0.938472942920682</v>
+        <v>0.9573758339510748</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9651229273870783</v>
+        <v>0.9747169811320755</v>
       </c>
       <c r="I5" t="n">
-        <v>57.24045443534851</v>
+        <v>35.65686535835266</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +584,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.05804768433489243</v>
+        <v>0.05958550649606533</v>
       </c>
       <c r="C6" t="n">
         <v>0.000996057350657239</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04707256053194139</v>
+        <v>0.07273349771689425</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9834633965068748</v>
+        <v>0.9751021924934968</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9794193311282616</v>
+        <v>0.9628158844765343</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9877687175685693</v>
+        <v>0.9885100074128984</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9835763055914375</v>
+        <v>0.9754937820043892</v>
       </c>
       <c r="I6" t="n">
-        <v>57.30775380134583</v>
+        <v>35.6390700340271</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +613,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.04184767329031124</v>
+        <v>0.04049713506583363</v>
       </c>
       <c r="C7" t="n">
         <v>0.0009938441702975688</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05569708481318725</v>
+        <v>0.08810838257147209</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9843924191750278</v>
+        <v>0.9652545522110739</v>
       </c>
       <c r="F7" t="n">
-        <v>0.988050784167289</v>
+        <v>0.9917743830787309</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9807264640474426</v>
+        <v>0.938472942920682</v>
       </c>
       <c r="H7" t="n">
-        <v>0.984375</v>
+        <v>0.9643877356693963</v>
       </c>
       <c r="I7" t="n">
-        <v>57.28160572052002</v>
+        <v>35.52160453796387</v>
       </c>
     </row>
     <row r="8">
@@ -654,28 +642,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03786633451053054</v>
+        <v>0.03736580572826034</v>
       </c>
       <c r="C8" t="n">
         <v>0.0009911436253643444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06744453422818195</v>
+        <v>0.05906599465710767</v>
       </c>
       <c r="E8" t="n">
-        <v>0.979933110367893</v>
+        <v>0.978446674098848</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9712518195050946</v>
+        <v>0.9781481481481481</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9892512972572276</v>
+        <v>0.9788732394366197</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9801689313257437</v>
+        <v>0.978510559466469</v>
       </c>
       <c r="I8" t="n">
-        <v>57.10372591018677</v>
+        <v>35.65112066268921</v>
       </c>
     </row>
     <row r="9">
@@ -683,28 +671,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.03422995920693567</v>
+        <v>0.03533232967304564</v>
       </c>
       <c r="C9" t="n">
         <v>0.0009879583809693736</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05187456539250668</v>
+        <v>0.0417313918090059</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9804905239687849</v>
+        <v>0.9873652917131178</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9872228485531755</v>
+        <v>0.9925093632958801</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9736842105263158</v>
+        <v>0.9822090437361009</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9804067923119985</v>
+        <v>0.9873323397913562</v>
       </c>
       <c r="I9" t="n">
-        <v>56.93190407752991</v>
+        <v>35.65987539291382</v>
       </c>
     </row>
     <row r="10">
@@ -712,28 +700,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02451803991289328</v>
+        <v>0.0295686050005564</v>
       </c>
       <c r="C10" t="n">
         <v>0.0009842915805643154</v>
       </c>
       <c r="D10" t="n">
-        <v>0.08847099976350978</v>
+        <v>0.04876993856860873</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9704570791527313</v>
+        <v>0.9838350055741361</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9832508564902931</v>
+        <v>0.9840563589173156</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9573758339510748</v>
+        <v>0.9836916234247591</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9701408450704225</v>
+        <v>0.9838739573679333</v>
       </c>
       <c r="I10" t="n">
-        <v>56.91925430297852</v>
+        <v>35.40626358985901</v>
       </c>
     </row>
     <row r="11">
@@ -741,28 +729,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02662775105028552</v>
+        <v>0.03015084790157261</v>
       </c>
       <c r="C11" t="n">
         <v>0.0009801468428384714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06505211525474064</v>
+        <v>0.04433968870507239</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9745447788926049</v>
+        <v>0.9830917874396136</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9961255327392483</v>
+        <v>0.9825990373935579</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9529280948851001</v>
+        <v>0.9836916234247591</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9740481151733282</v>
+        <v>0.9831450268568254</v>
       </c>
       <c r="I11" t="n">
-        <v>56.88703036308289</v>
+        <v>35.37901496887207</v>
       </c>
     </row>
     <row r="12">
@@ -770,28 +758,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02577176692092512</v>
+        <v>0.02331424339578064</v>
       </c>
       <c r="C12" t="n">
         <v>0.0009755282581475767</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04916779147585049</v>
+        <v>0.03905165118184947</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9842066146413972</v>
+        <v>0.9910813823857302</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9773474607234198</v>
+        <v>0.9900147928994083</v>
       </c>
       <c r="G12" t="n">
-        <v>0.991475166790215</v>
+        <v>0.9922164566345441</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9843606255749771</v>
+        <v>0.9911144020733061</v>
       </c>
       <c r="I12" t="n">
-        <v>56.91478633880615</v>
+        <v>35.31349897384644</v>
       </c>
     </row>
     <row r="13">
@@ -799,28 +787,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02050453400128469</v>
+        <v>0.02426905997631913</v>
       </c>
       <c r="C13" t="n">
         <v>0.0009704403844771127</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0231829335787864</v>
+        <v>0.0599123122583532</v>
       </c>
       <c r="E13" t="n">
-        <v>0.992196209587514</v>
+        <v>0.9812337421033073</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9882352941176471</v>
+        <v>0.9699601882012305</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9933283914010378</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9922480620155039</v>
+        <v>0.9815052188243911</v>
       </c>
       <c r="I13" t="n">
-        <v>57.52373337745667</v>
+        <v>35.69735479354858</v>
       </c>
     </row>
     <row r="14">
@@ -828,28 +816,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01975950884531054</v>
+        <v>0.02086871026347751</v>
       </c>
       <c r="C14" t="n">
         <v>0.0009648882429441257</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01831259087068042</v>
+        <v>0.03175610653947062</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9947974730583427</v>
+        <v>0.9895949461166852</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9970215934475056</v>
+        <v>0.9910780669144982</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9925871015567087</v>
+        <v>0.9881393624907339</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9947994056463596</v>
+        <v>0.9896065330363771</v>
       </c>
       <c r="I14" t="n">
-        <v>56.95065665245056</v>
+        <v>36.68217945098877</v>
       </c>
     </row>
     <row r="15">
@@ -857,28 +845,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02094901633848439</v>
+        <v>0.01624731523434377</v>
       </c>
       <c r="C15" t="n">
         <v>0.0009588773128419905</v>
       </c>
       <c r="D15" t="n">
-        <v>0.06132474881331603</v>
+        <v>0.05126289259118838</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9819769602378298</v>
+        <v>0.9843924191750278</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9689866570501262</v>
+        <v>0.9950757575757576</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9959229058561898</v>
+        <v>0.9736842105263158</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9822701517090111</v>
+        <v>0.9842637692019482</v>
       </c>
       <c r="I15" t="n">
-        <v>56.70845627784729</v>
+        <v>36.48184728622437</v>
       </c>
     </row>
     <row r="16">
@@ -886,28 +874,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01918828803111582</v>
+        <v>0.02057000931565812</v>
       </c>
       <c r="C16" t="n">
         <v>0.0009524135262330098</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02064077111034097</v>
+        <v>0.04621964955417241</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9936826458565589</v>
+        <v>0.9853214418431809</v>
       </c>
       <c r="F16" t="n">
-        <v>0.992603550295858</v>
+        <v>0.9958349110185536</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9948109710896961</v>
+        <v>0.9747961452928094</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9937060348019252</v>
+        <v>0.9852032215770744</v>
       </c>
       <c r="I16" t="n">
-        <v>56.86904907226562</v>
+        <v>36.42876648902893</v>
       </c>
     </row>
     <row r="17">
@@ -915,28 +903,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01749943079758725</v>
+        <v>0.02025096514079549</v>
       </c>
       <c r="C17" t="n">
         <v>0.0009455032620941839</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02445816856886628</v>
+        <v>0.05481367185160782</v>
       </c>
       <c r="E17" t="n">
-        <v>0.990709773318469</v>
+        <v>0.9786324786324786</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9878408253500368</v>
+        <v>0.9860745201354911</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9936990363232023</v>
+        <v>0.9710896960711638</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9907612712490761</v>
+        <v>0.9785247432306255</v>
       </c>
       <c r="I17" t="n">
-        <v>57.01095986366272</v>
+        <v>36.49957799911499</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +932,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01141035560992295</v>
+        <v>0.01364085715790092</v>
       </c>
       <c r="C18" t="n">
         <v>0.0009381533400219318</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02125176827510414</v>
+        <v>0.0532254194628107</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9931252322556671</v>
+        <v>0.9821627647714605</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9933259176863182</v>
+        <v>0.9943009118541033</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9929577464788732</v>
+        <v>0.9699777613046702</v>
       </c>
       <c r="H18" t="n">
-        <v>0.993141797961075</v>
+        <v>0.9819887429643527</v>
       </c>
       <c r="I18" t="n">
-        <v>57.15776920318604</v>
+        <v>36.63253593444824</v>
       </c>
     </row>
     <row r="19">
@@ -973,28 +961,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01432459629726655</v>
+        <v>0.0118536833765757</v>
       </c>
       <c r="C19" t="n">
         <v>0.0009303710135019719</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0389259072356162</v>
+        <v>0.01857680545873395</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9890375325157934</v>
+        <v>0.9940542549238202</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9828027808269301</v>
+        <v>0.9944362017804155</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9955522609340252</v>
+        <v>0.9936990363232023</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9891364389615173</v>
+        <v>0.9940674823878384</v>
       </c>
       <c r="I19" t="n">
-        <v>57.42335796356201</v>
+        <v>36.6676025390625</v>
       </c>
     </row>
     <row r="20">
@@ -1002,28 +990,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01445622746272431</v>
+        <v>0.01305335054678701</v>
       </c>
       <c r="C20" t="n">
         <v>0.0009221639627510076</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02183682405593142</v>
+        <v>0.02112649896759202</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9933110367892977</v>
+        <v>0.9938684503901896</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9929629629629629</v>
+        <v>0.9973870847331093</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9936990363232023</v>
+        <v>0.9903632320237212</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9933308632826973</v>
+        <v>0.9938627487446532</v>
       </c>
       <c r="I20" t="n">
-        <v>57.47102355957031</v>
+        <v>36.60255837440491</v>
       </c>
     </row>
     <row r="21">
@@ -1031,28 +1019,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01335378876333521</v>
+        <v>0.0142356286355722</v>
       </c>
       <c r="C21" t="n">
         <v>0.000913540287137281</v>
       </c>
       <c r="D21" t="n">
-        <v>0.02018950168402782</v>
+        <v>0.04835029222696645</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9940542549238202</v>
+        <v>0.986250464511334</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9944362017804155</v>
+        <v>0.9784828592268418</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9936990363232023</v>
+        <v>0.9944403261675315</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9940674823878384</v>
+        <v>0.9863970588235295</v>
       </c>
       <c r="I21" t="n">
-        <v>57.6183660030365</v>
+        <v>37.56696820259094</v>
       </c>
     </row>
     <row r="22">
@@ -1060,28 +1048,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01679229501461457</v>
+        <v>0.01458214992047075</v>
       </c>
       <c r="C22" t="n">
         <v>0.0009045084971874739</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01675430573184648</v>
+        <v>0.02393289202882443</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9944258639910813</v>
+        <v>0.9933110367892977</v>
       </c>
       <c r="F22" t="n">
-        <v>0.995910780669145</v>
+        <v>0.9947955390334573</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9929577464788732</v>
+        <v>0.9918458117123795</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9944320712694877</v>
+        <v>0.9933184855233853</v>
       </c>
       <c r="I22" t="n">
-        <v>57.1981840133667</v>
+        <v>36.7324013710022</v>
       </c>
     </row>
     <row r="23">
@@ -1089,28 +1077,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.006503388212848947</v>
+        <v>0.01118777208899231</v>
       </c>
       <c r="C23" t="n">
         <v>0.0008950775061878453</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01315057006544542</v>
+        <v>0.01643255995197746</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9959123002601263</v>
+        <v>0.9955406911928651</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9948224852071006</v>
+        <v>0.995919881305638</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9959274342835986</v>
+        <v>0.9955506117908788</v>
       </c>
       <c r="I23" t="n">
-        <v>57.10571098327637</v>
+        <v>36.55748105049133</v>
       </c>
     </row>
     <row r="24">
@@ -1118,28 +1106,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.003882327788473492</v>
+        <v>0.008232857585442462</v>
       </c>
       <c r="C24" t="n">
         <v>0.0008852566213878948</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01511707977737624</v>
+        <v>0.03191431244160746</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9966555183946488</v>
+        <v>0.9912671869193609</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9955621301775148</v>
+        <v>0.9966279505432747</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9859154929577465</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9966679007774898</v>
+        <v>0.9912427799515559</v>
       </c>
       <c r="I24" t="n">
-        <v>57.2160017490387</v>
+        <v>37.08141851425171</v>
       </c>
     </row>
     <row r="25">
@@ -1147,28 +1135,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.01148516741683634</v>
+        <v>0.01238943375651879</v>
       </c>
       <c r="C25" t="n">
         <v>0.0008750555348152299</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0254345930576412</v>
+        <v>0.03269819253884268</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9912671869193609</v>
+        <v>0.9901523597175771</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9922020051986632</v>
+        <v>0.9962476547842402</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9903632320237212</v>
+        <v>0.9840622683469237</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9912817659061398</v>
+        <v>0.9901174715644229</v>
       </c>
       <c r="I25" t="n">
-        <v>57.09860467910767</v>
+        <v>36.74834084510803</v>
       </c>
     </row>
     <row r="26">
@@ -1176,28 +1164,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01386099567908945</v>
+        <v>0.00778846624893249</v>
       </c>
       <c r="C26" t="n">
         <v>0.0008644843137107058</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0277351856497714</v>
+        <v>0.05378698963254223</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9914529914529915</v>
+        <v>0.9864362690449647</v>
       </c>
       <c r="F26" t="n">
-        <v>0.991475166790215</v>
+        <v>0.996219281663516</v>
       </c>
       <c r="G26" t="n">
-        <v>0.991475166790215</v>
+        <v>0.9766493699036323</v>
       </c>
       <c r="H26" t="n">
-        <v>0.991475166790215</v>
+        <v>0.9863372637095265</v>
       </c>
       <c r="I26" t="n">
-        <v>56.97389626502991</v>
+        <v>36.52573394775391</v>
       </c>
     </row>
     <row r="27">
@@ -1205,28 +1193,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01006347141507978</v>
+        <v>0.01204599678791653</v>
       </c>
       <c r="C27" t="n">
         <v>0.0008535533905932738</v>
       </c>
       <c r="D27" t="n">
-        <v>0.06952759125869247</v>
+        <v>0.02733275735769393</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9843924191750278</v>
+        <v>0.9908955778520996</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9954510993176648</v>
+        <v>0.9936638091688409</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9733135656041513</v>
+        <v>0.9881393624907339</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9842578710644677</v>
+        <v>0.9908938858948151</v>
       </c>
       <c r="I27" t="n">
-        <v>56.78659892082214</v>
+        <v>36.61095929145813</v>
       </c>
     </row>
     <row r="28">
@@ -1234,28 +1222,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.007975549239639897</v>
+        <v>0.007382693697499023</v>
       </c>
       <c r="C28" t="n">
         <v>0.0008422735529643445</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02585817095355169</v>
+        <v>0.02137216029514739</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9916387959866221</v>
+        <v>0.9940542549238202</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9889421304828603</v>
+        <v>0.996276991809382</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9944403261675315</v>
+        <v>0.9918458117123795</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9916836074662724</v>
+        <v>0.9940564635958395</v>
       </c>
       <c r="I28" t="n">
-        <v>56.97003436088562</v>
+        <v>36.72001361846924</v>
       </c>
     </row>
     <row r="29">
@@ -1263,28 +1251,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.00890871916882697</v>
+        <v>0.008199201023824485</v>
       </c>
       <c r="C29" t="n">
         <v>0.000830655932661826</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01363982299642228</v>
+        <v>0.01754174149663246</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9959123002601263</v>
+        <v>0.9960981047937569</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9929992630803243</v>
+        <v>0.996292176492399</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9988880652335063</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9959349593495935</v>
+        <v>0.9961075069508805</v>
       </c>
       <c r="I29" t="n">
-        <v>57.13302373886108</v>
+        <v>36.53641510009766</v>
       </c>
     </row>
     <row r="30">
@@ -1292,28 +1280,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01011861398920967</v>
+        <v>0.008347392449186683</v>
       </c>
       <c r="C30" t="n">
         <v>0.000818711994874345</v>
       </c>
       <c r="D30" t="n">
-        <v>0.05038597697963678</v>
+        <v>0.01613852945080622</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9858788554440728</v>
+        <v>0.9968413229282794</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9830508474576272</v>
+        <v>0.9970337411939192</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9888806523350631</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9859571322985957</v>
+        <v>0.9968489341983318</v>
       </c>
       <c r="I30" t="n">
-        <v>56.84075450897217</v>
+        <v>36.43937635421753</v>
       </c>
     </row>
     <row r="31">
@@ -1321,28 +1309,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.004613314400980325</v>
+        <v>0.006526745546221937</v>
       </c>
       <c r="C31" t="n">
         <v>0.0008064535268264884</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01714783257893242</v>
+        <v>0.01697899768348217</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9944258639910813</v>
+        <v>0.9953548866592344</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9933431952662722</v>
+        <v>0.9937199852234947</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9955522609340252</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9944465012958164</v>
+        <v>0.9953746530989824</v>
       </c>
       <c r="I31" t="n">
-        <v>56.74461126327515</v>
+        <v>36.68720483779907</v>
       </c>
     </row>
     <row r="32">
@@ -1350,28 +1338,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.006011033713666633</v>
+        <v>0.005654906970033236</v>
       </c>
       <c r="C32" t="n">
         <v>0.0007938926261462368</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02362938490538785</v>
+        <v>0.01710638058052582</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9923820141211446</v>
+        <v>0.9964697138610182</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9922193404964802</v>
+        <v>0.9959274342835986</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9925871015567087</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9924031869557162</v>
+        <v>0.9964808297832932</v>
       </c>
       <c r="I32" t="n">
-        <v>56.71149849891663</v>
+        <v>36.72017598152161</v>
       </c>
     </row>
     <row r="33">
@@ -1379,28 +1367,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.009712738071869828</v>
+        <v>0.01053825722468641</v>
       </c>
       <c r="C33" t="n">
         <v>0.0007810416889260655</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0285485384917092</v>
+        <v>0.0160221265605879</v>
       </c>
       <c r="E33" t="n">
-        <v>0.990709773318469</v>
+        <v>0.9955406911928651</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9966241560390098</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9848035581912528</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9906785980611484</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="I33" t="n">
-        <v>56.64529323577881</v>
+        <v>36.67858290672302</v>
       </c>
     </row>
     <row r="34">
@@ -1408,28 +1396,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.006507243329276733</v>
+        <v>0.004917657487186243</v>
       </c>
       <c r="C34" t="n">
         <v>0.0007679133974894984</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01714187273047878</v>
+        <v>0.02227423927200285</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9953548866592344</v>
+        <v>0.9947974730583427</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9940850277264325</v>
+        <v>0.9937130177514792</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9953729409587266</v>
+        <v>0.994816734542762</v>
       </c>
       <c r="I34" t="n">
-        <v>56.88565158843994</v>
+        <v>36.56785035133362</v>
       </c>
     </row>
     <row r="35">
@@ -1437,28 +1425,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.003673594506374969</v>
+        <v>0.005955092984648645</v>
       </c>
       <c r="C35" t="n">
         <v>0.0007545207078751858</v>
       </c>
       <c r="D35" t="n">
-        <v>0.009403583788965742</v>
+        <v>0.01217080044248904</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9977703455964325</v>
+        <v>0.9964697138610182</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9985152190051967</v>
+        <v>0.9940981187753597</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9988880652335063</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9977744807121661</v>
+        <v>0.9964873359216121</v>
       </c>
       <c r="I35" t="n">
-        <v>56.62401747703552</v>
+        <v>36.45059108734131</v>
       </c>
     </row>
     <row r="36">
@@ -1466,28 +1454,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.006067822750980328</v>
+        <v>0.005747231225721064</v>
       </c>
       <c r="C36" t="n">
         <v>0.0007408768370508578</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01032062398191352</v>
+        <v>0.01029092838920266</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9975845410628019</v>
+        <v>0.9972129319955407</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9966703662597114</v>
+        <v>0.9963004069552349</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9985174203113417</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9975930383262359</v>
+        <v>0.9972227365302722</v>
       </c>
       <c r="I36" t="n">
-        <v>56.52024340629578</v>
+        <v>36.56485986709595</v>
       </c>
     </row>
     <row r="37">
@@ -1495,28 +1483,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.003215680074020263</v>
+        <v>0.00897694934856447</v>
       </c>
       <c r="C37" t="n">
         <v>0.0007269952498697736</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01964458530405944</v>
+        <v>0.01176854212396053</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9946116685247121</v>
+        <v>0.9972129319955407</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9926172019195275</v>
+        <v>0.997773654916512</v>
       </c>
       <c r="G37" t="n">
         <v>0.9966641957005189</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9946365822082486</v>
+        <v>0.9972186167253848</v>
       </c>
       <c r="I37" t="n">
-        <v>56.54085326194763</v>
+        <v>36.88738870620728</v>
       </c>
     </row>
     <row r="38">
@@ -1524,28 +1512,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.005030980782839766</v>
+        <v>0.00168780749150988</v>
       </c>
       <c r="C38" t="n">
         <v>0.0007128896457825365</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01359004244535668</v>
+        <v>0.01160751208527262</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9949832775919732</v>
+        <v>0.9979561501300632</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9937153419593345</v>
+        <v>0.9966728280961183</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9992587101556709</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9950027762354248</v>
+        <v>0.9979640940218397</v>
       </c>
       <c r="I38" t="n">
-        <v>56.54072523117065</v>
+        <v>36.4832878112793</v>
       </c>
     </row>
     <row r="39">
@@ -1553,28 +1541,28 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.005897124316367604</v>
+        <v>0.005525023063373832</v>
       </c>
       <c r="C39" t="n">
         <v>0.0006985739453173904</v>
       </c>
       <c r="D39" t="n">
-        <v>0.009939016708124294</v>
+        <v>0.01688198275052166</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9972129319955407</v>
+        <v>0.9957264957264957</v>
       </c>
       <c r="F39" t="n">
-        <v>0.997773654916512</v>
+        <v>0.9962894248608535</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9972186167253848</v>
+        <v>0.9957352123122566</v>
       </c>
       <c r="I39" t="n">
-        <v>56.46969532966614</v>
+        <v>36.6482081413269</v>
       </c>
     </row>
     <row r="40">
@@ -1582,28 +1570,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.002466777180055277</v>
+        <v>0.006634801873640708</v>
       </c>
       <c r="C40" t="n">
         <v>0.0006840622763423392</v>
       </c>
       <c r="D40" t="n">
-        <v>0.01049654216594126</v>
+        <v>0.0192346679808982</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9977703455964325</v>
+        <v>0.9947974730583427</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9981454005934718</v>
+        <v>0.9937130177514792</v>
       </c>
       <c r="G40" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9977753058954394</v>
+        <v>0.994816734542762</v>
       </c>
       <c r="I40" t="n">
-        <v>56.88503122329712</v>
+        <v>36.44402027130127</v>
       </c>
     </row>
     <row r="41">
@@ -1611,28 +1599,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>0.004901881205681054</v>
+        <v>0.00243026394892299</v>
       </c>
       <c r="C41" t="n">
         <v>0.0006693689601226459</v>
       </c>
       <c r="D41" t="n">
-        <v>0.02176060155267897</v>
+        <v>0.0211887273049883</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9942400594574508</v>
+        <v>0.9929394277220365</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9962783773725344</v>
+        <v>0.9977544910179641</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9922164566345441</v>
+        <v>0.9881393624907339</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9942432683379758</v>
+        <v>0.9929236499068901</v>
       </c>
       <c r="I41" t="n">
-        <v>56.81190967559814</v>
+        <v>36.42354679107666</v>
       </c>
     </row>
     <row r="42">
@@ -1640,28 +1628,28 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.005337211361288806</v>
+        <v>0.005996767658399609</v>
       </c>
       <c r="C42" t="n">
         <v>0.0006545084971874739</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0146412002794819</v>
+        <v>0.0172306816507363</v>
       </c>
       <c r="E42" t="n">
-        <v>0.99702712746191</v>
+        <v>0.9955406911928651</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9937223042836041</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9955604883462819</v>
       </c>
       <c r="I42" t="n">
-        <v>56.75482821464539</v>
+        <v>36.67402958869934</v>
       </c>
     </row>
     <row r="43">
@@ -1669,28 +1657,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.0001030754729288439</v>
+        <v>0.00462054030858686</v>
       </c>
       <c r="C43" t="n">
         <v>0.0006394955530196148</v>
       </c>
       <c r="D43" t="n">
-        <v>0.01875294882132593</v>
+        <v>0.03026983257952786</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9964697138610182</v>
+        <v>0.9894091415830546</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9981405727036073</v>
+        <v>0.9958693203154337</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9948109710896961</v>
+        <v>0.9829503335804299</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9964729905327641</v>
+        <v>0.9893676552881925</v>
       </c>
       <c r="I43" t="n">
-        <v>56.64678049087524</v>
+        <v>36.72636556625366</v>
       </c>
     </row>
     <row r="44">
@@ -1698,28 +1686,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.008580022139565066</v>
+        <v>0.004120457604396484</v>
       </c>
       <c r="C44" t="n">
         <v>0.0006243449435824275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.01009216008411203</v>
+        <v>0.00939497974090605</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9959123002601263</v>
+        <v>0.9981419546636938</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9944567627494457</v>
+        <v>0.9966740576496674</v>
       </c>
       <c r="G44" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9996293550778355</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9959289415247965</v>
+        <v>0.9981495188749074</v>
       </c>
       <c r="I44" t="n">
-        <v>56.71549940109253</v>
+        <v>36.60147500038147</v>
       </c>
     </row>
     <row r="45">
@@ -1727,28 +1715,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.003081310769080342</v>
+        <v>0.001727419341553477</v>
       </c>
       <c r="C45" t="n">
         <v>0.0006090716206982715</v>
       </c>
       <c r="D45" t="n">
-        <v>0.01395475054948142</v>
+        <v>0.008023026438880114</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9964697138610182</v>
+        <v>0.9977703455964325</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9962949240459429</v>
+        <v>0.9966715976331361</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9988880652335063</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9964795256624051</v>
+        <v>0.9977786005183266</v>
       </c>
       <c r="I45" t="n">
-        <v>57.03666591644287</v>
+        <v>36.50728940963745</v>
       </c>
     </row>
     <row r="46">
@@ -1756,28 +1744,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>0.004389823063883899</v>
+        <v>0.001394095049400212</v>
       </c>
       <c r="C46" t="n">
         <v>0.0005936906572928626</v>
       </c>
       <c r="D46" t="n">
-        <v>0.005259956500325772</v>
+        <v>0.01111704149799588</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9977703455964325</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9955588452997779</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9962962962962963</v>
       </c>
       <c r="I46" t="n">
-        <v>56.62359499931335</v>
+        <v>36.59389734268188</v>
       </c>
     </row>
     <row r="47">
@@ -1785,28 +1773,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.001472115522713508</v>
+        <v>0.005711103450937115</v>
       </c>
       <c r="C47" t="n">
         <v>0.0005782172325201157</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01560295344558207</v>
+        <v>0.01517164235469298</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9959123002601263</v>
+        <v>0.9946116685247121</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9970282317979198</v>
+        <v>0.9981336319522209</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9948109710896961</v>
+        <v>0.9911045218680504</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9959183673469387</v>
+        <v>0.9946066579877255</v>
       </c>
       <c r="I47" t="n">
-        <v>56.89182424545288</v>
+        <v>36.51397967338562</v>
       </c>
     </row>
     <row r="48">
@@ -1814,28 +1802,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.003562437480427819</v>
+        <v>0.002731720100566173</v>
       </c>
       <c r="C48" t="n">
         <v>0.0005626666167821524</v>
       </c>
       <c r="D48" t="n">
-        <v>0.006247523102561743</v>
+        <v>0.008111003440510276</v>
       </c>
       <c r="E48" t="n">
         <v>0.9981419546636938</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9985163204747775</v>
+        <v>0.9974093264248705</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9988880652335063</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9981460882461994</v>
+        <v>0.9981481481481481</v>
       </c>
       <c r="I48" t="n">
-        <v>57.03870058059692</v>
+        <v>36.54358601570129</v>
       </c>
     </row>
     <row r="49">
@@ -1843,28 +1831,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.003914304320521173</v>
+        <v>5.117069653249423e-05</v>
       </c>
       <c r="C49" t="n">
         <v>0.0005470541566592573</v>
       </c>
       <c r="D49" t="n">
-        <v>0.006039735738744445</v>
+        <v>0.008895857024192443</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9975845410628019</v>
+        <v>0.9981419546636938</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9959364610269671</v>
+        <v>0.9974093264248705</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9992587101556709</v>
+        <v>0.9988880652335063</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9975948196114709</v>
+        <v>0.9981481481481481</v>
       </c>
       <c r="I49" t="n">
-        <v>56.85762023925781</v>
+        <v>36.50030398368835</v>
       </c>
     </row>
     <row r="50">
@@ -1872,28 +1860,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0006630882056232829</v>
+        <v>1.060158760331292e-05</v>
       </c>
       <c r="C50" t="n">
         <v>0.000531395259764657</v>
       </c>
       <c r="D50" t="n">
-        <v>0.007117764273237342</v>
+        <v>0.009669220793256104</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9979561501300632</v>
+        <v>0.9981419546636938</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9974083672713809</v>
+        <v>0.9977777777777778</v>
       </c>
       <c r="G50" t="n">
         <v>0.9985174203113417</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9979625856640119</v>
+        <v>0.9981474620229714</v>
       </c>
       <c r="I50" t="n">
-        <v>56.66686105728149</v>
+        <v>35.74145007133484</v>
       </c>
     </row>
     <row r="51">
@@ -1901,28 +1889,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.004142391625174832</v>
+        <v>7.831003521039985e-06</v>
       </c>
       <c r="C51" t="n">
         <v>0.0005157053795390644</v>
       </c>
       <c r="D51" t="n">
-        <v>0.01544754707923556</v>
+        <v>0.01008746845601961</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9957264957264957</v>
+        <v>0.9981419546636938</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9981378026070763</v>
+        <v>0.9977777777777778</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.9985174203113417</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9957272896154561</v>
+        <v>0.9981474620229714</v>
       </c>
       <c r="I51" t="n">
-        <v>56.92185068130493</v>
+        <v>35.43676733970642</v>
       </c>
     </row>
   </sheetData>
